--- a/samples/sample_3/SAFE_VESSELS_INDEX_20251201.XLSX
+++ b/samples/sample_3/SAFE_VESSELS_INDEX_20251201.XLSX
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t xml:space="preserve">SHIPID</t>
   </si>
@@ -54,22 +54,22 @@
     <t xml:space="preserve">NOTE3</t>
   </si>
   <si>
-    <t xml:space="preserve">SH_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big Ship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUST_001  </t>
+    <t xml:space="preserve">ship 01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eagle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cust 001</t>
   </si>
   <si>
     <t xml:space="preserve">A</t>
   </si>
   <si>
-    <t xml:space="preserve">bigdog@email.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brain@email.com</t>
+    <t xml:space="preserve">eagle@test.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bird@test.com</t>
   </si>
   <si>
     <t xml:space="preserve">BUN                                                         </t>
@@ -78,19 +78,25 @@
     <t xml:space="preserve">AMS</t>
   </si>
   <si>
-    <t xml:space="preserve">FUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fast Ship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUST_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fastdog@email.com</t>
+    <t xml:space="preserve">ship 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawk@test.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ship 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">falcon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9009003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">falcon@test.com</t>
   </si>
 </sst>
 </file>
@@ -174,20 +180,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -383,7 +385,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.14"/>
@@ -397,7 +399,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="6.85"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -429,7 +431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -451,25 +453,22 @@
       <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="1" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>9009002</v>
@@ -478,25 +477,54 @@
         <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="bigdog@email.com"/>
-    <hyperlink ref="G2" r:id="rId2" display="brain@email"/>
-    <hyperlink ref="F3" r:id="rId3" display="fastdog@email.com"/>
-    <hyperlink ref="G3" r:id="rId4" display="brain@email"/>
+    <hyperlink ref="F2" r:id="rId1" display="eagle@test.com"/>
+    <hyperlink ref="G2" r:id="rId2" display="bird@test.com"/>
+    <hyperlink ref="F3" r:id="rId3" display="hawk@test.com"/>
+    <hyperlink ref="G3" r:id="rId4" display="bird@test.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -514,7 +542,7 @@
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -532,7 +560,7 @@
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/samples/sample_3/SAFE_VESSELS_INDEX_20251201.XLSX
+++ b/samples/sample_3/SAFE_VESSELS_INDEX_20251201.XLSX
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t xml:space="preserve">SHIPID</t>
   </si>
@@ -87,10 +87,13 @@
     <t xml:space="preserve">hawk@test.com</t>
   </si>
   <si>
-    <t xml:space="preserve">ship 03</t>
+    <t xml:space="preserve">ship 00</t>
   </si>
   <si>
     <t xml:space="preserve">falcon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cust 002</t>
   </si>
   <si>
     <t xml:space="preserve">9009003</t>
@@ -185,11 +188,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -497,16 +500,16 @@
         <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>15</v>
